--- a/Yeni_Strateji_15m_30m_Sonuclari.xlsx
+++ b/Yeni_Strateji_15m_30m_Sonuclari.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,37 +463,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DENGE</t>
+          <t>A1YEN</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.81</v>
+        <v>1.52</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>30 Dakikalık</t>
+          <t>15 Dakikalık</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="E2" t="n">
-        <v>1.68</v>
+        <v>1.51</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-30 15:30:00</t>
+          <t>2026-09-30 16:00:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DURKN</t>
+          <t>CRFSA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10.59</v>
+        <v>190.2</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -501,51 +501,51 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>49.32</v>
+        <v>53.57</v>
       </c>
       <c r="E3" t="n">
-        <v>10.56</v>
+        <v>189.25</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-30 15:30:00</t>
+          <t>2026-09-30 16:00:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ETYAT</t>
+          <t>DMSAS</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10.15</v>
+        <v>6.14</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>15 Dakikalık</t>
+          <t>30 Dakikalık</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>61.48</v>
+        <v>61.22</v>
       </c>
       <c r="E4" t="n">
-        <v>9.92</v>
+        <v>6.03</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-30 15:30:00</t>
+          <t>2026-09-30 16:00:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MSGYO</t>
+          <t>EFOR</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.97</v>
+        <v>13.53</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -553,51 +553,51 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>59.09</v>
+        <v>58.82</v>
       </c>
       <c r="E5" t="n">
-        <v>4.93</v>
+        <v>13.48</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-30 15:30:00</t>
+          <t>2026-09-30 16:00:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PRKAB</t>
+          <t>ERBOS</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>24.14</v>
+        <v>115.4</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>15 Dakikalık</t>
+          <t>30 Dakikalık</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>53.33</v>
+        <v>50</v>
       </c>
       <c r="E6" t="n">
-        <v>24.1</v>
+        <v>115.09</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-30 15:30:00</t>
+          <t>2026-09-30 16:00:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>YGGYO</t>
+          <t>GOLDA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>211</v>
+        <v>7.63</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -605,14 +605,118 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>64.79000000000001</v>
+        <v>58.33</v>
       </c>
       <c r="E7" t="n">
-        <v>208.55</v>
+        <v>7.59</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-30 15:30:00</t>
+          <t>2026-09-30 16:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>GOLDA</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>7.63</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>30 Dakikalık</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="E8" t="n">
+        <v>7.59</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-09-30 16:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>OYLUM</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>15 Dakikalık</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="E9" t="n">
+        <v>6.09</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-09-30 16:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>TUCLK</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>15 Dakikalık</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>53.49</v>
+      </c>
+      <c r="E10" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-09-30 16:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>TUCLK</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>30 Dakikalık</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>53.97</v>
+      </c>
+      <c r="E11" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-09-30 16:00:00</t>
         </is>
       </c>
     </row>

--- a/Yeni_Strateji_15m_30m_Sonuclari.xlsx
+++ b/Yeni_Strateji_15m_30m_Sonuclari.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -489,22 +489,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CRFSA</t>
+          <t>DMSAS</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>190.2</v>
+        <v>6.08</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>15 Dakikalık</t>
+          <t>30 Dakikalık</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>53.57</v>
+        <v>58.7</v>
       </c>
       <c r="E3" t="n">
-        <v>189.25</v>
+        <v>6.03</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -515,22 +515,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DMSAS</t>
+          <t>ERBOS</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.14</v>
+        <v>115.6</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>30 Dakikalık</t>
+          <t>15 Dakikalık</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>61.22</v>
+        <v>54.69</v>
       </c>
       <c r="E4" t="n">
-        <v>6.03</v>
+        <v>115.22</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -541,22 +541,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>EFOR</t>
+          <t>ERBOS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13.53</v>
+        <v>115.6</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>15 Dakikalık</t>
+          <t>30 Dakikalık</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>58.82</v>
+        <v>51.72</v>
       </c>
       <c r="E5" t="n">
-        <v>13.48</v>
+        <v>115.1</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -567,11 +567,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ERBOS</t>
+          <t>GOLDA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>115.4</v>
+        <v>7.61</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -579,10 +579,10 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>50</v>
+        <v>51.39</v>
       </c>
       <c r="E6" t="n">
-        <v>115.09</v>
+        <v>7.59</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -593,22 +593,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GOLDA</t>
+          <t>TUCLK</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.63</v>
+        <v>4.57</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>15 Dakikalık</t>
+          <t>30 Dakikalık</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>58.33</v>
+        <v>56.06</v>
       </c>
       <c r="E7" t="n">
-        <v>7.59</v>
+        <v>4.47</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -619,11 +619,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GOLDA</t>
+          <t>VANGD</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7.63</v>
+        <v>53.9</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -631,90 +631,12 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>52.7</v>
+        <v>60.24</v>
       </c>
       <c r="E8" t="n">
-        <v>7.59</v>
+        <v>51.39</v>
       </c>
       <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-09-30 16:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>OYLUM</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>6.17</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>15 Dakikalık</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>62.5</v>
-      </c>
-      <c r="E9" t="n">
-        <v>6.09</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-09-30 16:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>TUCLK</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>4.54</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>15 Dakikalık</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>53.49</v>
-      </c>
-      <c r="E10" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-09-30 16:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>TUCLK</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>4.54</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>30 Dakikalık</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>53.97</v>
-      </c>
-      <c r="E11" t="n">
-        <v>4.47</v>
-      </c>
-      <c r="F11" t="inlineStr">
         <is>
           <t>2026-09-30 16:00:00</t>
         </is>

--- a/Yeni_Strateji_15m_30m_Sonuclari.xlsx
+++ b/Yeni_Strateji_15m_30m_Sonuclari.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,182 +463,26 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A1YEN</t>
+          <t>TGSAS</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.52</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>15 Dakikalık</t>
+          <t>30 Dakikalık</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>50</v>
+        <v>70.31999999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>1.51</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-30 16:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>DMSAS</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>6.08</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>30 Dakikalık</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>58.7</v>
-      </c>
-      <c r="E3" t="n">
-        <v>6.03</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>2026-09-30 16:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>ERBOS</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>115.6</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>15 Dakikalık</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>54.69</v>
-      </c>
-      <c r="E4" t="n">
-        <v>115.22</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>2026-09-30 16:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>ERBOS</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>115.6</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>30 Dakikalık</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>51.72</v>
-      </c>
-      <c r="E5" t="n">
-        <v>115.1</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2026-09-30 16:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>GOLDA</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>7.61</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>30 Dakikalık</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>51.39</v>
-      </c>
-      <c r="E6" t="n">
-        <v>7.59</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-09-30 16:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>TUCLK</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>4.57</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>30 Dakikalık</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>56.06</v>
-      </c>
-      <c r="E7" t="n">
-        <v>4.47</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-09-30 16:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>VANGD</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>53.9</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>30 Dakikalık</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>60.24</v>
-      </c>
-      <c r="E8" t="n">
-        <v>51.39</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-09-30 16:00:00</t>
+          <t>2026-09-30 16:30:00</t>
         </is>
       </c>
     </row>

--- a/Yeni_Strateji_15m_30m_Sonuclari.xlsx
+++ b/Yeni_Strateji_15m_30m_Sonuclari.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,24 +463,102 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>DOFER</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>20.96</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>15 Dakikalık</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>57.63</v>
+      </c>
+      <c r="E2" t="n">
+        <v>20.91</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-09-30 16:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>MSGYO</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>15 Dakikalık</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>55.56</v>
+      </c>
+      <c r="E3" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-09-30 16:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>TGSAS</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>85.09999999999999</v>
-      </c>
-      <c r="C2" t="inlineStr">
+      <c r="B4" t="n">
+        <v>88.09999999999999</v>
+      </c>
+      <c r="C4" t="inlineStr">
         <is>
           <t>30 Dakikalık</t>
         </is>
       </c>
-      <c r="D2" t="n">
-        <v>70.31999999999999</v>
-      </c>
-      <c r="E2" t="n">
-        <v>84.09999999999999</v>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="D4" t="n">
+        <v>74.69</v>
+      </c>
+      <c r="E4" t="n">
+        <v>84.25</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-09-30 16:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>VANGD</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>53.65</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>30 Dakikalık</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>76.36</v>
+      </c>
+      <c r="E5" t="n">
+        <v>51.6</v>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>2026-09-30 16:30:00</t>
         </is>

--- a/Yeni_Strateji_15m_30m_Sonuclari.xlsx
+++ b/Yeni_Strateji_15m_30m_Sonuclari.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,37 +463,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DOFER</t>
+          <t>ADEL</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20.96</v>
+        <v>24.22</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>15 Dakikalık</t>
+          <t>30 Dakikalık</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>57.63</v>
+        <v>56.52</v>
       </c>
       <c r="E2" t="n">
-        <v>20.91</v>
+        <v>24.07</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-30 16:30:00</t>
+          <t>2026-09-30 17:00:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MSGYO</t>
+          <t>BTCIM</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.01</v>
+        <v>1.89</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -501,66 +501,352 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>55.56</v>
+        <v>56.25</v>
       </c>
       <c r="E3" t="n">
-        <v>4.94</v>
+        <v>1.88</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-30 16:30:00</t>
+          <t>2026-09-30 17:00:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TGSAS</t>
+          <t>ECZYT</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>88.09999999999999</v>
+        <v>221.7</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>30 Dakikalık</t>
+          <t>15 Dakikalık</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>74.69</v>
+        <v>60.78</v>
       </c>
       <c r="E4" t="n">
-        <v>84.25</v>
+        <v>219.62</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-30 16:30:00</t>
+          <t>2026-09-30 17:00:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>VANGD</t>
+          <t>KRDMA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>53.65</v>
+        <v>39.42</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>15 Dakikalık</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>51.83</v>
+      </c>
+      <c r="E5" t="n">
+        <v>39.02</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-09-30 17:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>LMKDC</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>23.54</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>15 Dakikalık</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>68.18000000000001</v>
+      </c>
+      <c r="E6" t="n">
+        <v>23.04</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-09-30 17:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>LMKDC</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>23.54</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>30 Dakikalık</t>
         </is>
       </c>
-      <c r="D5" t="n">
-        <v>76.36</v>
-      </c>
-      <c r="E5" t="n">
-        <v>51.6</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2026-09-30 16:30:00</t>
+      <c r="D7" t="n">
+        <v>51.04</v>
+      </c>
+      <c r="E7" t="n">
+        <v>23.19</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-09-30 17:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>OZKGY</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>12.06</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>30 Dakikalık</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>50</v>
+      </c>
+      <c r="E8" t="n">
+        <v>12.04</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-09-30 17:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>PATEK</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>13.72</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>15 Dakikalık</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>60.89</v>
+      </c>
+      <c r="E9" t="n">
+        <v>13.35</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-09-30 17:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>REEDR</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>15 Dakikalık</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>56.36</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-09-30 17:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SANFM</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>15 Dakikalık</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>75</v>
+      </c>
+      <c r="E11" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-09-30 17:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>SANFM</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>30 Dakikalık</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>63.24</v>
+      </c>
+      <c r="E12" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-09-30 17:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>SEYKM</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>30 Dakikalık</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>72.45999999999999</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-09-30 17:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>SUNTK</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>25.04</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>15 Dakikalık</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>50.68</v>
+      </c>
+      <c r="E14" t="n">
+        <v>24.83</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-09-30 17:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>TKFEN</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>231.1</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>15 Dakikalık</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>58.12</v>
+      </c>
+      <c r="E15" t="n">
+        <v>224.75</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-09-30 17:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>TKFEN</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>231.1</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>30 Dakikalık</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>57.17</v>
+      </c>
+      <c r="E16" t="n">
+        <v>229.49</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-09-30 17:00:00</t>
         </is>
       </c>
     </row>
